--- a/ventas_ejemplo_Excel.xlsx
+++ b/ventas_ejemplo_Excel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\$alfonso\Proyectos\files\Lumina_Ant\Lumina_Ant\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EF92531-FDA5-43F5-B024-939C8AA84A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A93DAE59-D188-4908-ADEE-8C0009D3849A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{98B03C18-A374-4444-9253-BD78B4DBE274}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9944" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10624" uniqueCount="78">
   <si>
     <t>fecha</t>
   </si>
@@ -256,6 +256,18 @@
   </si>
   <si>
     <t>Energía</t>
+  </si>
+  <si>
+    <t>Silla Ergonómica</t>
+  </si>
+  <si>
+    <t>Auriculares Jabra</t>
+  </si>
+  <si>
+    <t>Proyector Epson</t>
+  </si>
+  <si>
+    <t>Presentación</t>
   </si>
 </sst>
 </file>
@@ -1115,9 +1127,31 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="4">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{F6F7BB4A-DF68-4BC2-ACCF-C916AC27FBC3}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;db0116a5-b2c5-4968-a71a-e435d5cae7ff&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D72A7CB-2B1D-4B92-A075-834DE6429E0E}">
-  <dimension ref="A1:H2485"/>
+  <dimension ref="A1:H2655"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -65346,337 +65380,337 @@
     </row>
     <row r="2471" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2471" s="1">
-        <v>46067</v>
+        <v>46071</v>
       </c>
       <c r="B2471" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="C2471" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="D2471">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E2471">
-        <v>656.82</v>
+        <v>1722.47</v>
       </c>
       <c r="F2471">
-        <v>5911.38</v>
+        <v>1722.47</v>
       </c>
       <c r="G2471" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="H2471" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2472" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2472" s="1">
-        <v>46068</v>
+        <v>46071</v>
       </c>
       <c r="B2472" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="C2472" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="D2472">
         <v>7</v>
       </c>
       <c r="E2472">
-        <v>6421.31</v>
+        <v>4189.55</v>
       </c>
       <c r="F2472">
-        <v>44949.17</v>
+        <v>29326.85</v>
       </c>
       <c r="G2472" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H2472" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2473" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2473" s="1">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B2473" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="C2473" t="s">
-        <v>59</v>
+        <v>9</v>
       </c>
       <c r="D2473">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E2473">
-        <v>1347.45</v>
+        <v>12543.21</v>
       </c>
       <c r="F2473">
-        <v>6737.25</v>
+        <v>37629.629999999997</v>
       </c>
       <c r="G2473" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H2473" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2474" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2474" s="1">
-        <v>46069</v>
+        <v>46072</v>
       </c>
       <c r="B2474" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C2474" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D2474">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E2474">
-        <v>1634.62</v>
+        <v>867.28</v>
       </c>
       <c r="F2474">
-        <v>14711.58</v>
+        <v>3469.12</v>
       </c>
       <c r="G2474" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="H2474" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2475" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2475" s="1">
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="B2475" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="C2475" t="s">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="D2475">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E2475">
-        <v>1815.99</v>
+        <v>4661.49</v>
       </c>
       <c r="F2475">
-        <v>9079.9500000000007</v>
+        <v>9322.98</v>
       </c>
       <c r="G2475" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="H2475" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2476" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2476" s="1">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B2476" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C2476" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D2476">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E2476">
-        <v>1815.99</v>
+        <v>2115.42</v>
       </c>
       <c r="F2476">
-        <v>9079.9500000000007</v>
+        <v>8461.68</v>
       </c>
       <c r="G2476" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H2476" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2477" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2477" s="1">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B2477" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C2477" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D2477">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2477">
-        <v>1815.99</v>
+        <v>12985.33</v>
       </c>
       <c r="F2477">
-        <v>9079.9500000000007</v>
+        <v>77911.98</v>
       </c>
       <c r="G2477" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="H2477" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2478" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2478" s="1">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B2478" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="C2478" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="D2478">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E2478">
-        <v>1815.99</v>
+        <v>641.54999999999995</v>
       </c>
       <c r="F2478">
-        <v>9079.9500000000007</v>
+        <v>1924.65</v>
       </c>
       <c r="G2478" t="s">
         <v>18</v>
       </c>
       <c r="H2478" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2479" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2479" s="1">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B2479" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="C2479" t="s">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="D2479">
         <v>5</v>
       </c>
       <c r="E2479">
-        <v>1815.99</v>
+        <v>3098.76</v>
       </c>
       <c r="F2479">
-        <v>9079.9500000000007</v>
+        <v>15493.8</v>
       </c>
       <c r="G2479" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H2479" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2480" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2480" s="1">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B2480" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="C2480" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="D2480">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E2480">
-        <v>1815.99</v>
+        <v>5712.44</v>
       </c>
       <c r="F2480">
-        <v>9079.9500000000007</v>
+        <v>17137.32</v>
       </c>
       <c r="G2480" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="H2480" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2481" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2481" s="1">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B2481" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="C2481" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="D2481">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2481">
-        <v>1815.99</v>
+        <v>1421.33</v>
       </c>
       <c r="F2481">
-        <v>9079.9500000000007</v>
+        <v>8527.98</v>
       </c>
       <c r="G2481" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="H2481" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2482" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2482" s="1">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="B2482" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="C2482" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D2482">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E2482">
-        <v>1815.99</v>
+        <v>6554.21</v>
       </c>
       <c r="F2482">
-        <v>9079.9500000000007</v>
+        <v>26216.84</v>
       </c>
       <c r="G2482" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="H2482" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2483" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2483" s="1">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="B2483" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C2483" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="D2483">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E2483">
-        <v>1815.99</v>
+        <v>2087.65</v>
       </c>
       <c r="F2483">
-        <v>9079.9500000000007</v>
+        <v>16701.2</v>
       </c>
       <c r="G2483" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="H2483" t="s">
         <v>72</v>
@@ -65684,54 +65718,4474 @@
     </row>
     <row r="2484" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2484" s="1">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="B2484" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="C2484" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="D2484">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E2484">
-        <v>1815.99</v>
+        <v>3712.88</v>
       </c>
       <c r="F2484">
-        <v>9079.9500000000007</v>
+        <v>11138.64</v>
       </c>
       <c r="G2484" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H2484" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2485" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2485" s="1">
-        <v>46071</v>
+        <v>46074</v>
       </c>
       <c r="B2485" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2485" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2485">
+        <v>2</v>
+      </c>
+      <c r="E2485">
+        <v>7321.44</v>
+      </c>
+      <c r="F2485">
+        <v>14642.88</v>
+      </c>
+      <c r="G2485" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2485" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2486" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2486" s="1">
+        <v>46075</v>
+      </c>
+      <c r="B2486" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2486" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2486">
+        <v>5</v>
+      </c>
+      <c r="E2486">
+        <v>2788.33</v>
+      </c>
+      <c r="F2486">
+        <v>13941.65</v>
+      </c>
+      <c r="G2486" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2486" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2487" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2487" s="1">
+        <v>46075</v>
+      </c>
+      <c r="B2487" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2487" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2487">
+        <v>7</v>
+      </c>
+      <c r="E2487">
+        <v>1145.22</v>
+      </c>
+      <c r="F2487">
+        <v>8016.54</v>
+      </c>
+      <c r="G2487" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2487" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2488" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2488" s="1">
+        <v>46075</v>
+      </c>
+      <c r="B2488" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2488" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2488">
+        <v>3</v>
+      </c>
+      <c r="E2488">
+        <v>13122.77</v>
+      </c>
+      <c r="F2488">
+        <v>39368.31</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2488" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2489" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2489" s="1">
+        <v>46075</v>
+      </c>
+      <c r="B2489" t="s">
         <v>26</v>
       </c>
-      <c r="C2485" t="s">
+      <c r="C2489" t="s">
         <v>27</v>
       </c>
-      <c r="D2485">
+      <c r="D2489">
+        <v>6</v>
+      </c>
+      <c r="E2489">
+        <v>1834.55</v>
+      </c>
+      <c r="F2489">
+        <v>11007.3</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2489" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2490" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2490" s="1">
+        <v>46076</v>
+      </c>
+      <c r="B2490" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2490" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2490">
         <v>5</v>
       </c>
-      <c r="E2485">
-        <v>1815.99</v>
-      </c>
-      <c r="F2485">
-        <v>9079.9500000000007</v>
-      </c>
-      <c r="G2485" t="s">
+      <c r="E2490">
+        <v>2088.44</v>
+      </c>
+      <c r="F2490">
+        <v>10442.200000000001</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2490" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2491" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2491" s="1">
+        <v>46076</v>
+      </c>
+      <c r="B2491" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2491" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2491">
+        <v>3</v>
+      </c>
+      <c r="E2491">
+        <v>192.33</v>
+      </c>
+      <c r="F2491">
+        <v>576.99</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2491" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2492" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2492" s="1">
+        <v>46076</v>
+      </c>
+      <c r="B2492" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2492" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2492">
+        <v>2</v>
+      </c>
+      <c r="E2492">
+        <v>3788.66</v>
+      </c>
+      <c r="F2492">
+        <v>7577.32</v>
+      </c>
+      <c r="G2492" t="s">
         <v>18</v>
       </c>
-      <c r="H2485" t="s">
+      <c r="H2492" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2493" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2493" s="1">
+        <v>46076</v>
+      </c>
+      <c r="B2493" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2493" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2493">
+        <v>9</v>
+      </c>
+      <c r="E2493">
+        <v>1677.88</v>
+      </c>
+      <c r="F2493">
+        <v>15100.92</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2493" t="s">
         <v>72</v>
+      </c>
+    </row>
+    <row r="2494" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2494" s="1">
+        <v>46077</v>
+      </c>
+      <c r="B2494" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2494" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2494">
+        <v>1</v>
+      </c>
+      <c r="E2494">
+        <v>8455.33</v>
+      </c>
+      <c r="F2494">
+        <v>8455.33</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2494" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2495" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2495" s="1">
+        <v>46077</v>
+      </c>
+      <c r="B2495" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2495" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2495">
+        <v>6</v>
+      </c>
+      <c r="E2495">
+        <v>7188.22</v>
+      </c>
+      <c r="F2495">
+        <v>43129.32</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2495" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2496" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2496" s="1">
+        <v>46077</v>
+      </c>
+      <c r="B2496" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2496" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2496">
+        <v>4</v>
+      </c>
+      <c r="E2496">
+        <v>2044.11</v>
+      </c>
+      <c r="F2496">
+        <v>8176.44</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2496" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2497" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2497" s="1">
+        <v>46078</v>
+      </c>
+      <c r="B2497" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2497" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2497">
+        <v>7</v>
+      </c>
+      <c r="E2497">
+        <v>5844.77</v>
+      </c>
+      <c r="F2497">
+        <v>40913.39</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2497" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2498" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2498" s="1">
+        <v>46078</v>
+      </c>
+      <c r="B2498" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2498" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2498">
+        <v>3</v>
+      </c>
+      <c r="E2498">
+        <v>3155.44</v>
+      </c>
+      <c r="F2498">
+        <v>9466.32</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>48</v>
+      </c>
+      <c r="H2498" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2499" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2499" s="1">
+        <v>46078</v>
+      </c>
+      <c r="B2499" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2499" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2499">
+        <v>8</v>
+      </c>
+      <c r="E2499">
+        <v>1388.22</v>
+      </c>
+      <c r="F2499">
+        <v>11105.76</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2499" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2500" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2500" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B2500" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2500" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2500">
+        <v>5</v>
+      </c>
+      <c r="E2500">
+        <v>6511.88</v>
+      </c>
+      <c r="F2500">
+        <v>32559.4</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2500" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2501" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2501" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B2501" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2501" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2501">
+        <v>4</v>
+      </c>
+      <c r="E2501">
+        <v>688.44</v>
+      </c>
+      <c r="F2501">
+        <v>2753.76</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2501" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2502" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2502" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B2502" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2502" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2502">
+        <v>2</v>
+      </c>
+      <c r="E2502">
+        <v>4322.66</v>
+      </c>
+      <c r="F2502">
+        <v>8645.32</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2502" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2503" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2503" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B2503" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2503" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2503">
+        <v>1</v>
+      </c>
+      <c r="E2503">
+        <v>12677.33</v>
+      </c>
+      <c r="F2503">
+        <v>12677.33</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2503" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2504" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2504" s="1">
+        <v>46080</v>
+      </c>
+      <c r="B2504" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2504" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2504">
+        <v>6</v>
+      </c>
+      <c r="E2504">
+        <v>912.55</v>
+      </c>
+      <c r="F2504">
+        <v>5475.3</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2504" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2505" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2505" s="1">
+        <v>46080</v>
+      </c>
+      <c r="B2505" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2505" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2505">
+        <v>4</v>
+      </c>
+      <c r="E2505">
+        <v>4533.88</v>
+      </c>
+      <c r="F2505">
+        <v>18135.52</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2505" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2506" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2506" s="1">
+        <v>46080</v>
+      </c>
+      <c r="B2506" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2506" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2506">
+        <v>3</v>
+      </c>
+      <c r="E2506">
+        <v>1766.44</v>
+      </c>
+      <c r="F2506">
+        <v>5299.32</v>
+      </c>
+      <c r="G2506" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2506" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2507" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2507" s="1">
+        <v>46081</v>
+      </c>
+      <c r="B2507" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2507" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2507">
+        <v>7</v>
+      </c>
+      <c r="E2507">
+        <v>2155.33</v>
+      </c>
+      <c r="F2507">
+        <v>15087.31</v>
+      </c>
+      <c r="G2507" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2507" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2508" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2508" s="1">
+        <v>46081</v>
+      </c>
+      <c r="B2508" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2508" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2508">
+        <v>5</v>
+      </c>
+      <c r="E2508">
+        <v>1188.77</v>
+      </c>
+      <c r="F2508">
+        <v>5943.85</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2508" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2509" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2509" s="1">
+        <v>46081</v>
+      </c>
+      <c r="B2509" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2509" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2509">
+        <v>9</v>
+      </c>
+      <c r="E2509">
+        <v>2211.44</v>
+      </c>
+      <c r="F2509">
+        <v>19902.96</v>
+      </c>
+      <c r="G2509" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2509" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2510" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2510" s="1">
+        <v>46082</v>
+      </c>
+      <c r="B2510" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2510" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2510">
+        <v>3</v>
+      </c>
+      <c r="E2510">
+        <v>2933.22</v>
+      </c>
+      <c r="F2510">
+        <v>8799.66</v>
+      </c>
+      <c r="G2510" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2510" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2511" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2511" s="1">
+        <v>46082</v>
+      </c>
+      <c r="B2511" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2511" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2511">
+        <v>6</v>
+      </c>
+      <c r="E2511">
+        <v>3655.88</v>
+      </c>
+      <c r="F2511">
+        <v>21935.279999999999</v>
+      </c>
+      <c r="G2511" t="s">
+        <v>48</v>
+      </c>
+      <c r="H2511" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2512" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2512" s="1">
+        <v>46082</v>
+      </c>
+      <c r="B2512" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2512" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2512">
+        <v>2</v>
+      </c>
+      <c r="E2512">
+        <v>5577.44</v>
+      </c>
+      <c r="F2512">
+        <v>11154.88</v>
+      </c>
+      <c r="G2512" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2512" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2513" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2513" s="1">
+        <v>46082</v>
+      </c>
+      <c r="B2513" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2513" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2513">
+        <v>8</v>
+      </c>
+      <c r="E2513">
+        <v>185.55</v>
+      </c>
+      <c r="F2513">
+        <v>1484.4</v>
+      </c>
+      <c r="G2513" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2513" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2514" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2514" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B2514" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2514" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2514">
+        <v>5</v>
+      </c>
+      <c r="E2514">
+        <v>7444.22</v>
+      </c>
+      <c r="F2514">
+        <v>37221.1</v>
+      </c>
+      <c r="G2514" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2514" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2515" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2515" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B2515" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2515" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2515">
+        <v>7</v>
+      </c>
+      <c r="E2515">
+        <v>1722.33</v>
+      </c>
+      <c r="F2515">
+        <v>12056.31</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2515" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2516" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2516" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B2516" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2516" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2516">
+        <v>4</v>
+      </c>
+      <c r="E2516">
+        <v>13244.88</v>
+      </c>
+      <c r="F2516">
+        <v>52979.519999999997</v>
+      </c>
+      <c r="G2516" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2516" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2517" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2517" s="1">
+        <v>46084</v>
+      </c>
+      <c r="B2517" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2517" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2517">
+        <v>8</v>
+      </c>
+      <c r="E2517">
+        <v>2977.44</v>
+      </c>
+      <c r="F2517">
+        <v>23819.52</v>
+      </c>
+      <c r="G2517" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2517" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2518" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2518" s="1">
+        <v>46084</v>
+      </c>
+      <c r="B2518" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2518" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2518">
+        <v>3</v>
+      </c>
+      <c r="E2518">
+        <v>1455.66</v>
+      </c>
+      <c r="F2518">
+        <v>4366.9799999999996</v>
+      </c>
+      <c r="G2518" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2518" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2519" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2519" s="1">
+        <v>46084</v>
+      </c>
+      <c r="B2519" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2519" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2519">
+        <v>6</v>
+      </c>
+      <c r="E2519">
+        <v>6388.77</v>
+      </c>
+      <c r="F2519">
+        <v>38332.620000000003</v>
+      </c>
+      <c r="G2519" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2519" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2520" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2520" s="1">
+        <v>46085</v>
+      </c>
+      <c r="B2520" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2520" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2520">
+        <v>10</v>
+      </c>
+      <c r="E2520">
+        <v>655.33000000000004</v>
+      </c>
+      <c r="F2520">
+        <v>6553.3</v>
+      </c>
+      <c r="G2520" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2520" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2521" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2521" s="1">
+        <v>46085</v>
+      </c>
+      <c r="B2521" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2521" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2521">
+        <v>4</v>
+      </c>
+      <c r="E2521">
+        <v>3655.22</v>
+      </c>
+      <c r="F2521">
+        <v>14620.88</v>
+      </c>
+      <c r="G2521" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2521" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2522" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2522" s="1">
+        <v>46085</v>
+      </c>
+      <c r="B2522" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2522" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2522">
+        <v>3</v>
+      </c>
+      <c r="E2522">
+        <v>4188.66</v>
+      </c>
+      <c r="F2522">
+        <v>12565.98</v>
+      </c>
+      <c r="G2522" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2522" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2523" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2523" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B2523" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2523" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2523">
+        <v>2</v>
+      </c>
+      <c r="E2523">
+        <v>8788.44</v>
+      </c>
+      <c r="F2523">
+        <v>17576.88</v>
+      </c>
+      <c r="G2523" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2523" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2524" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2524" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B2524" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2524" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2524">
+        <v>6</v>
+      </c>
+      <c r="E2524">
+        <v>2088.2199999999998</v>
+      </c>
+      <c r="F2524">
+        <v>12529.32</v>
+      </c>
+      <c r="G2524" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2524" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2525" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2525" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B2525" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2525" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2525">
+        <v>4</v>
+      </c>
+      <c r="E2525">
+        <v>2033.55</v>
+      </c>
+      <c r="F2525">
+        <v>8134.2</v>
+      </c>
+      <c r="G2525" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2525" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2526" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2526" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B2526" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2526" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2526">
+        <v>7</v>
+      </c>
+      <c r="E2526">
+        <v>1811.33</v>
+      </c>
+      <c r="F2526">
+        <v>12679.31</v>
+      </c>
+      <c r="G2526" t="s">
+        <v>48</v>
+      </c>
+      <c r="H2526" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2527" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2527" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B2527" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2527" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2527">
+        <v>5</v>
+      </c>
+      <c r="E2527">
+        <v>5711.88</v>
+      </c>
+      <c r="F2527">
+        <v>28559.4</v>
+      </c>
+      <c r="G2527" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2527" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2528" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2528" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B2528" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2528" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2528">
+        <v>3</v>
+      </c>
+      <c r="E2528">
+        <v>4788.22</v>
+      </c>
+      <c r="F2528">
+        <v>14364.66</v>
+      </c>
+      <c r="G2528" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2528" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2529" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2529" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B2529" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2529" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2529">
+        <v>8</v>
+      </c>
+      <c r="E2529">
+        <v>888.44</v>
+      </c>
+      <c r="F2529">
+        <v>7107.52</v>
+      </c>
+      <c r="G2529" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2529" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2530" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2530" s="1">
+        <v>46088</v>
+      </c>
+      <c r="B2530" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2530" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2530">
+        <v>7</v>
+      </c>
+      <c r="E2530">
+        <v>12533.44</v>
+      </c>
+      <c r="F2530">
+        <v>87734.080000000002</v>
+      </c>
+      <c r="G2530" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2530" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2531" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2531" s="1">
+        <v>46088</v>
+      </c>
+      <c r="B2531" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2531" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2531">
+        <v>4</v>
+      </c>
+      <c r="E2531">
+        <v>1133.22</v>
+      </c>
+      <c r="F2531">
+        <v>4532.88</v>
+      </c>
+      <c r="G2531" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2531" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2532" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2532" s="1">
+        <v>46088</v>
+      </c>
+      <c r="B2532" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2532" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2532">
+        <v>6</v>
+      </c>
+      <c r="E2532">
+        <v>193.77</v>
+      </c>
+      <c r="F2532">
+        <v>1162.6199999999999</v>
+      </c>
+      <c r="G2532" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2532" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2533" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2533" s="1">
+        <v>46089</v>
+      </c>
+      <c r="B2533" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2533" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2533">
+        <v>3</v>
+      </c>
+      <c r="E2533">
+        <v>6722.11</v>
+      </c>
+      <c r="F2533">
+        <v>20166.330000000002</v>
+      </c>
+      <c r="G2533" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2533" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2534" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2534" s="1">
+        <v>46089</v>
+      </c>
+      <c r="B2534" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2534" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2534">
+        <v>5</v>
+      </c>
+      <c r="E2534">
+        <v>3788.44</v>
+      </c>
+      <c r="F2534">
+        <v>18942.2</v>
+      </c>
+      <c r="G2534" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2534" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2535" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2535" s="1">
+        <v>46089</v>
+      </c>
+      <c r="B2535" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2535" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2535">
+        <v>4</v>
+      </c>
+      <c r="E2535">
+        <v>2855.66</v>
+      </c>
+      <c r="F2535">
+        <v>11422.64</v>
+      </c>
+      <c r="G2535" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2535" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2536" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2536" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B2536" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2536" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2536">
+        <v>9</v>
+      </c>
+      <c r="E2536">
+        <v>1322.88</v>
+      </c>
+      <c r="F2536">
+        <v>11905.92</v>
+      </c>
+      <c r="G2536" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2536" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2537" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2537" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B2537" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2537" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2537">
+        <v>6</v>
+      </c>
+      <c r="E2537">
+        <v>3044.55</v>
+      </c>
+      <c r="F2537">
+        <v>18267.3</v>
+      </c>
+      <c r="G2537" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2537" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2538" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2538" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B2538" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2538" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2538">
+        <v>3</v>
+      </c>
+      <c r="E2538">
+        <v>7266.88</v>
+      </c>
+      <c r="F2538">
+        <v>21800.639999999999</v>
+      </c>
+      <c r="G2538" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2538" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2539" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2539" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B2539" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2539" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2539">
+        <v>5</v>
+      </c>
+      <c r="E2539">
+        <v>1588.77</v>
+      </c>
+      <c r="F2539">
+        <v>7943.85</v>
+      </c>
+      <c r="G2539" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2539" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2540" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2540" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B2540" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2540" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2540">
+        <v>8</v>
+      </c>
+      <c r="E2540">
+        <v>4277.33</v>
+      </c>
+      <c r="F2540">
+        <v>34218.639999999999</v>
+      </c>
+      <c r="G2540" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2540" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2541" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2541" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B2541" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2541" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2541">
+        <v>3</v>
+      </c>
+      <c r="E2541">
+        <v>2133.44</v>
+      </c>
+      <c r="F2541">
+        <v>6400.32</v>
+      </c>
+      <c r="G2541" t="s">
+        <v>48</v>
+      </c>
+      <c r="H2541" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2542" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2542" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B2542" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2542" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2542">
+        <v>6</v>
+      </c>
+      <c r="E2542">
+        <v>2177.66</v>
+      </c>
+      <c r="F2542">
+        <v>13065.96</v>
+      </c>
+      <c r="G2542" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2542" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2543" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2543" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B2543" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2543" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2543">
+        <v>4</v>
+      </c>
+      <c r="E2543">
+        <v>5633.11</v>
+      </c>
+      <c r="F2543">
+        <v>22532.44</v>
+      </c>
+      <c r="G2543" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2543" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2544" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2544" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B2544" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2544" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2544">
+        <v>7</v>
+      </c>
+      <c r="E2544">
+        <v>672.44</v>
+      </c>
+      <c r="F2544">
+        <v>4707.08</v>
+      </c>
+      <c r="G2544" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2544" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2545" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2545" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B2545" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2545" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2545">
+        <v>3</v>
+      </c>
+      <c r="E2545">
+        <v>3888.22</v>
+      </c>
+      <c r="F2545">
+        <v>11664.66</v>
+      </c>
+      <c r="G2545" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2545" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2546" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2546" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B2546" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2546" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2546">
+        <v>5</v>
+      </c>
+      <c r="E2546">
+        <v>12888.55</v>
+      </c>
+      <c r="F2546">
+        <v>64442.75</v>
+      </c>
+      <c r="G2546" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2546" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2547" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2547" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B2547" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2547" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2547">
+        <v>6</v>
+      </c>
+      <c r="E2547">
+        <v>1155.8800000000001</v>
+      </c>
+      <c r="F2547">
+        <v>6935.28</v>
+      </c>
+      <c r="G2547" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2547" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2548" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2548" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B2548" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2548" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2548">
+        <v>8</v>
+      </c>
+      <c r="E2548">
+        <v>6455.33</v>
+      </c>
+      <c r="F2548">
+        <v>51642.64</v>
+      </c>
+      <c r="G2548" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2548" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2549" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2549" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B2549" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2549" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2549">
+        <v>3</v>
+      </c>
+      <c r="E2549">
+        <v>8222.44</v>
+      </c>
+      <c r="F2549">
+        <v>24667.32</v>
+      </c>
+      <c r="G2549" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2549" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2550" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2550" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B2550" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2550" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2550">
+        <v>5</v>
+      </c>
+      <c r="E2550">
+        <v>4666.7700000000004</v>
+      </c>
+      <c r="F2550">
+        <v>23333.85</v>
+      </c>
+      <c r="G2550" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2550" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2551" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2551" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B2551" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2551" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2551">
+        <v>4</v>
+      </c>
+      <c r="E2551">
+        <v>1755.22</v>
+      </c>
+      <c r="F2551">
+        <v>7020.88</v>
+      </c>
+      <c r="G2551" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2551" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2552" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2552" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B2552" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2552" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2552">
+        <v>7</v>
+      </c>
+      <c r="E2552">
+        <v>3722.88</v>
+      </c>
+      <c r="F2552">
+        <v>26060.16</v>
+      </c>
+      <c r="G2552" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2552" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2553" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2553" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B2553" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2553" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2553">
+        <v>4</v>
+      </c>
+      <c r="E2553">
+        <v>1488.33</v>
+      </c>
+      <c r="F2553">
+        <v>5953.32</v>
+      </c>
+      <c r="G2553" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2553" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2554" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2554" s="1">
+        <v>46095</v>
+      </c>
+      <c r="B2554" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2554" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2554">
+        <v>9</v>
+      </c>
+      <c r="E2554">
+        <v>933.44</v>
+      </c>
+      <c r="F2554">
+        <v>8400.9599999999991</v>
+      </c>
+      <c r="G2554" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2554" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2555" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2555" s="1">
+        <v>46096</v>
+      </c>
+      <c r="B2555" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2555" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2555">
+        <v>4</v>
+      </c>
+      <c r="E2555">
+        <v>3211.55</v>
+      </c>
+      <c r="F2555">
+        <v>12846.2</v>
+      </c>
+      <c r="G2555" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2555" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2556" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2556" s="1">
+        <v>46096</v>
+      </c>
+      <c r="B2556" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2556" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2556">
+        <v>6</v>
+      </c>
+      <c r="E2556">
+        <v>4355.88</v>
+      </c>
+      <c r="F2556">
+        <v>26135.279999999999</v>
+      </c>
+      <c r="G2556" t="s">
+        <v>48</v>
+      </c>
+      <c r="H2556" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2557" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2557" s="1">
+        <v>46096</v>
+      </c>
+      <c r="B2557" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2557" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2557">
+        <v>5</v>
+      </c>
+      <c r="E2557">
+        <v>188.77</v>
+      </c>
+      <c r="F2557">
+        <v>943.85</v>
+      </c>
+      <c r="G2557" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2557" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2558" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2558" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B2558" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2558" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2558">
+        <v>7</v>
+      </c>
+      <c r="E2558">
+        <v>2055.66</v>
+      </c>
+      <c r="F2558">
+        <v>14389.62</v>
+      </c>
+      <c r="G2558" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2558" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2559" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2559" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B2559" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2559" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2559">
+        <v>4</v>
+      </c>
+      <c r="E2559">
+        <v>7533.22</v>
+      </c>
+      <c r="F2559">
+        <v>30132.880000000001</v>
+      </c>
+      <c r="G2559" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2559" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2560" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2560" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B2560" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2560" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2560">
+        <v>6</v>
+      </c>
+      <c r="E2560">
+        <v>2711.44</v>
+      </c>
+      <c r="F2560">
+        <v>16268.64</v>
+      </c>
+      <c r="G2560" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2560" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2561" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2561" s="1">
+        <v>46098</v>
+      </c>
+      <c r="B2561" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2561" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2561">
+        <v>8</v>
+      </c>
+      <c r="E2561">
+        <v>13011.33</v>
+      </c>
+      <c r="F2561">
+        <v>104090.64</v>
+      </c>
+      <c r="G2561" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2561" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2562" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2562" s="1">
+        <v>46098</v>
+      </c>
+      <c r="B2562" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2562" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2562">
+        <v>3</v>
+      </c>
+      <c r="E2562">
+        <v>2066.77</v>
+      </c>
+      <c r="F2562">
+        <v>6200.31</v>
+      </c>
+      <c r="G2562" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2562" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2563" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2563" s="1">
+        <v>46098</v>
+      </c>
+      <c r="B2563" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2563" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2563">
+        <v>6</v>
+      </c>
+      <c r="E2563">
+        <v>1644.55</v>
+      </c>
+      <c r="F2563">
+        <v>9867.2999999999993</v>
+      </c>
+      <c r="G2563" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2563" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2564" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2564" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B2564" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2564" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2564">
+        <v>9</v>
+      </c>
+      <c r="E2564">
+        <v>5488.88</v>
+      </c>
+      <c r="F2564">
+        <v>49399.92</v>
+      </c>
+      <c r="G2564" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2564" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2565" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2565" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B2565" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2565" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2565">
+        <v>5</v>
+      </c>
+      <c r="E2565">
+        <v>677.33</v>
+      </c>
+      <c r="F2565">
+        <v>3386.65</v>
+      </c>
+      <c r="G2565" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2565" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2566" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2566" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B2566" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2566" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2566">
+        <v>7</v>
+      </c>
+      <c r="E2566">
+        <v>6611.44</v>
+      </c>
+      <c r="F2566">
+        <v>46280.08</v>
+      </c>
+      <c r="G2566" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2566" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2567" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2567" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B2567" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2567" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2567">
+        <v>5</v>
+      </c>
+      <c r="E2567">
+        <v>3744.66</v>
+      </c>
+      <c r="F2567">
+        <v>18723.3</v>
+      </c>
+      <c r="G2567" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2567" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2568" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2568" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B2568" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2568" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2568">
+        <v>8</v>
+      </c>
+      <c r="E2568">
+        <v>1177.33</v>
+      </c>
+      <c r="F2568">
+        <v>9418.64</v>
+      </c>
+      <c r="G2568" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2568" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2569" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2569" s="1">
+        <v>46101</v>
+      </c>
+      <c r="B2569" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2569" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2569">
+        <v>6</v>
+      </c>
+      <c r="E2569">
+        <v>7088.44</v>
+      </c>
+      <c r="F2569">
+        <v>42530.64</v>
+      </c>
+      <c r="G2569" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2569" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2570" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2570" s="1">
+        <v>46101</v>
+      </c>
+      <c r="B2570" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2570" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2570">
+        <v>4</v>
+      </c>
+      <c r="E2570">
+        <v>1822.55</v>
+      </c>
+      <c r="F2570">
+        <v>7290.2</v>
+      </c>
+      <c r="G2570" t="s">
+        <v>48</v>
+      </c>
+      <c r="H2570" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2571" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2571" s="1">
+        <v>46101</v>
+      </c>
+      <c r="B2571" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2571" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2571">
+        <v>2</v>
+      </c>
+      <c r="E2571">
+        <v>4455.88</v>
+      </c>
+      <c r="F2571">
+        <v>8911.76</v>
+      </c>
+      <c r="G2571" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2571" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2572" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2572" s="1">
+        <v>46102</v>
+      </c>
+      <c r="B2572" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2572" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2572">
+        <v>5</v>
+      </c>
+      <c r="E2572">
+        <v>2177.66</v>
+      </c>
+      <c r="F2572">
+        <v>10888.3</v>
+      </c>
+      <c r="G2572" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2572" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2573" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2573" s="1">
+        <v>46102</v>
+      </c>
+      <c r="B2573" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2573" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2573">
+        <v>10</v>
+      </c>
+      <c r="E2573">
+        <v>191.44</v>
+      </c>
+      <c r="F2573">
+        <v>1914.4</v>
+      </c>
+      <c r="G2573" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2573" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2574" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2574" s="1">
+        <v>46102</v>
+      </c>
+      <c r="B2574" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2574" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2574">
+        <v>3</v>
+      </c>
+      <c r="E2574">
+        <v>2966.88</v>
+      </c>
+      <c r="F2574">
+        <v>8900.64</v>
+      </c>
+      <c r="G2574" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2574" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2575" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2575" s="1">
+        <v>46103</v>
+      </c>
+      <c r="B2575" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2575" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2575">
+        <v>6</v>
+      </c>
+      <c r="E2575">
+        <v>12744.55</v>
+      </c>
+      <c r="F2575">
+        <v>76467.3</v>
+      </c>
+      <c r="G2575" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2575" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2576" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2576" s="1">
+        <v>46103</v>
+      </c>
+      <c r="B2576" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2576" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2576">
+        <v>4</v>
+      </c>
+      <c r="E2576">
+        <v>3088.22</v>
+      </c>
+      <c r="F2576">
+        <v>12352.88</v>
+      </c>
+      <c r="G2576" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2576" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2577" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2577" s="1">
+        <v>46103</v>
+      </c>
+      <c r="B2577" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2577" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2577">
+        <v>8</v>
+      </c>
+      <c r="E2577">
+        <v>3566.77</v>
+      </c>
+      <c r="F2577">
+        <v>28534.16</v>
+      </c>
+      <c r="G2577" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2577" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2578" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2578" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B2578" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2578" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2578">
+        <v>7</v>
+      </c>
+      <c r="E2578">
+        <v>1411.33</v>
+      </c>
+      <c r="F2578">
+        <v>9879.31</v>
+      </c>
+      <c r="G2578" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2578" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2579" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2579" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B2579" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2579" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2579">
+        <v>5</v>
+      </c>
+      <c r="E2579">
+        <v>4233.4399999999996</v>
+      </c>
+      <c r="F2579">
+        <v>21167.200000000001</v>
+      </c>
+      <c r="G2579" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2579" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2580" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2580" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B2580" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2580" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2580">
+        <v>2</v>
+      </c>
+      <c r="E2580">
+        <v>8555.2199999999993</v>
+      </c>
+      <c r="F2580">
+        <v>17110.439999999999</v>
+      </c>
+      <c r="G2580" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2580" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2581" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2581" s="1">
+        <v>46105</v>
+      </c>
+      <c r="B2581" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2581" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2581">
+        <v>8</v>
+      </c>
+      <c r="E2581">
+        <v>1711.88</v>
+      </c>
+      <c r="F2581">
+        <v>13695.04</v>
+      </c>
+      <c r="G2581" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2581" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2582" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2582" s="1">
+        <v>46105</v>
+      </c>
+      <c r="B2582" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2582" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2582">
+        <v>3</v>
+      </c>
+      <c r="E2582">
+        <v>2144.33</v>
+      </c>
+      <c r="F2582">
+        <v>6432.99</v>
+      </c>
+      <c r="G2582" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2582" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2583" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2583" s="1">
+        <v>46105</v>
+      </c>
+      <c r="B2583" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2583" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2583">
+        <v>6</v>
+      </c>
+      <c r="E2583">
+        <v>5566.44</v>
+      </c>
+      <c r="F2583">
+        <v>33398.639999999999</v>
+      </c>
+      <c r="G2583" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2583" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2584" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2584" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B2584" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2584" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2584">
+        <v>4</v>
+      </c>
+      <c r="E2584">
+        <v>664.77</v>
+      </c>
+      <c r="F2584">
+        <v>2659.08</v>
+      </c>
+      <c r="G2584" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2584" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2585" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2585" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B2585" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2585" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2585">
+        <v>7</v>
+      </c>
+      <c r="E2585">
+        <v>911.22</v>
+      </c>
+      <c r="F2585">
+        <v>6378.54</v>
+      </c>
+      <c r="G2585" t="s">
+        <v>48</v>
+      </c>
+      <c r="H2585" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2586" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2586" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B2586" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2586" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2586">
+        <v>5</v>
+      </c>
+      <c r="E2586">
+        <v>6733.55</v>
+      </c>
+      <c r="F2586">
+        <v>33667.75</v>
+      </c>
+      <c r="G2586" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2586" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2587" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2587" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B2587" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2587" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2587">
+        <v>6</v>
+      </c>
+      <c r="E2587">
+        <v>2099.44</v>
+      </c>
+      <c r="F2587">
+        <v>12596.64</v>
+      </c>
+      <c r="G2587" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2587" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2588" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2588" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B2588" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2588" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2588">
+        <v>3</v>
+      </c>
+      <c r="E2588">
+        <v>7455.88</v>
+      </c>
+      <c r="F2588">
+        <v>22367.64</v>
+      </c>
+      <c r="G2588" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2588" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2589" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2589" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B2589" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2589" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2589">
+        <v>4</v>
+      </c>
+      <c r="E2589">
+        <v>12399.22</v>
+      </c>
+      <c r="F2589">
+        <v>49596.88</v>
+      </c>
+      <c r="G2589" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2589" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2590" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2590" s="1">
+        <v>46108</v>
+      </c>
+      <c r="B2590" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2590" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2590">
+        <v>9</v>
+      </c>
+      <c r="E2590">
+        <v>1122.6600000000001</v>
+      </c>
+      <c r="F2590">
+        <v>10103.94</v>
+      </c>
+      <c r="G2590" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2590" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2591" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2591" s="1">
+        <v>46108</v>
+      </c>
+      <c r="B2591" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2591" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2591">
+        <v>4</v>
+      </c>
+      <c r="E2591">
+        <v>3811.44</v>
+      </c>
+      <c r="F2591">
+        <v>15245.76</v>
+      </c>
+      <c r="G2591" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2591" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2592" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2592" s="1">
+        <v>46108</v>
+      </c>
+      <c r="B2592" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2592" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2592">
+        <v>6</v>
+      </c>
+      <c r="E2592">
+        <v>1788.33</v>
+      </c>
+      <c r="F2592">
+        <v>10729.98</v>
+      </c>
+      <c r="G2592" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2592" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2593" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2593" s="1">
+        <v>46109</v>
+      </c>
+      <c r="B2593" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2593" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2593">
+        <v>7</v>
+      </c>
+      <c r="E2593">
+        <v>2944.55</v>
+      </c>
+      <c r="F2593">
+        <v>20611.849999999999</v>
+      </c>
+      <c r="G2593" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2593" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2594" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2594" s="1">
+        <v>46109</v>
+      </c>
+      <c r="B2594" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2594" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2594">
+        <v>5</v>
+      </c>
+      <c r="E2594">
+        <v>5699.88</v>
+      </c>
+      <c r="F2594">
+        <v>28499.4</v>
+      </c>
+      <c r="G2594" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2594" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2595" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2595" s="1">
+        <v>46109</v>
+      </c>
+      <c r="B2595" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2595" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2595">
+        <v>2</v>
+      </c>
+      <c r="E2595">
+        <v>2833.22</v>
+      </c>
+      <c r="F2595">
+        <v>5666.44</v>
+      </c>
+      <c r="G2595" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2595" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2596" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2596" s="1">
+        <v>46110</v>
+      </c>
+      <c r="B2596" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2596" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2596">
+        <v>8</v>
+      </c>
+      <c r="E2596">
+        <v>1399.77</v>
+      </c>
+      <c r="F2596">
+        <v>11198.16</v>
+      </c>
+      <c r="G2596" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2596" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2597" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2597" s="1">
+        <v>46110</v>
+      </c>
+      <c r="B2597" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2597" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2597">
+        <v>3</v>
+      </c>
+      <c r="E2597">
+        <v>3922.44</v>
+      </c>
+      <c r="F2597">
+        <v>11767.32</v>
+      </c>
+      <c r="G2597" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2597" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2598" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2598" s="1">
+        <v>46110</v>
+      </c>
+      <c r="B2598" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2598" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2598">
+        <v>6</v>
+      </c>
+      <c r="E2598">
+        <v>186.88</v>
+      </c>
+      <c r="F2598">
+        <v>1121.28</v>
+      </c>
+      <c r="G2598" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2598" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2599" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2599" s="1">
+        <v>46111</v>
+      </c>
+      <c r="B2599" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2599" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2599">
+        <v>4</v>
+      </c>
+      <c r="E2599">
+        <v>4311.55</v>
+      </c>
+      <c r="F2599">
+        <v>17246.2</v>
+      </c>
+      <c r="G2599" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2599" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2600" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2600" s="1">
+        <v>46111</v>
+      </c>
+      <c r="B2600" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2600" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2600">
+        <v>8</v>
+      </c>
+      <c r="E2600">
+        <v>2133.2199999999998</v>
+      </c>
+      <c r="F2600">
+        <v>17065.759999999998</v>
+      </c>
+      <c r="G2600" t="s">
+        <v>48</v>
+      </c>
+      <c r="H2600" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2601" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2601" s="1">
+        <v>46111</v>
+      </c>
+      <c r="B2601" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2601" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2601">
+        <v>3</v>
+      </c>
+      <c r="E2601">
+        <v>1699.44</v>
+      </c>
+      <c r="F2601">
+        <v>5098.32</v>
+      </c>
+      <c r="G2601" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2601" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2602" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2602" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B2602" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2602" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2602">
+        <v>9</v>
+      </c>
+      <c r="E2602">
+        <v>13055.66</v>
+      </c>
+      <c r="F2602">
+        <v>117500.94</v>
+      </c>
+      <c r="G2602" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2602" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2603" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2603" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B2603" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2603" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2603">
+        <v>6</v>
+      </c>
+      <c r="E2603">
+        <v>4577.88</v>
+      </c>
+      <c r="F2603">
+        <v>27467.279999999999</v>
+      </c>
+      <c r="G2603" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2603" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2604" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2604" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B2604" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2604" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2604">
+        <v>1</v>
+      </c>
+      <c r="E2604">
+        <v>8644.33</v>
+      </c>
+      <c r="F2604">
+        <v>8644.33</v>
+      </c>
+      <c r="G2604" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2604" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2605" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2605" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B2605" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2605" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2605">
+        <v>4</v>
+      </c>
+      <c r="E2605">
+        <v>6488.77</v>
+      </c>
+      <c r="F2605">
+        <v>25955.08</v>
+      </c>
+      <c r="G2605" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2605" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2606" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2606" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B2606" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2606" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2606">
+        <v>8</v>
+      </c>
+      <c r="E2606">
+        <v>671.55</v>
+      </c>
+      <c r="F2606">
+        <v>5372.4</v>
+      </c>
+      <c r="G2606" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2606" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2607" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2607" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B2607" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2607" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2607">
+        <v>5</v>
+      </c>
+      <c r="E2607">
+        <v>899.22</v>
+      </c>
+      <c r="F2607">
+        <v>4496.1000000000004</v>
+      </c>
+      <c r="G2607" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2607" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2608" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2608" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B2608" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2608" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2608">
+        <v>3</v>
+      </c>
+      <c r="E2608">
+        <v>2166.88</v>
+      </c>
+      <c r="F2608">
+        <v>6500.64</v>
+      </c>
+      <c r="G2608" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2608" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2609" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2609" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B2609" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2609" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2609">
+        <v>7</v>
+      </c>
+      <c r="E2609">
+        <v>3699.44</v>
+      </c>
+      <c r="F2609">
+        <v>25895.08</v>
+      </c>
+      <c r="G2609" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2609" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2610" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2610" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B2610" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2610" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2610">
+        <v>9</v>
+      </c>
+      <c r="E2610">
+        <v>7211.33</v>
+      </c>
+      <c r="F2610">
+        <v>64901.97</v>
+      </c>
+      <c r="G2610" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2610" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2611" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2611" s="1">
+        <v>46115</v>
+      </c>
+      <c r="B2611" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2611" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2611">
+        <v>5</v>
+      </c>
+      <c r="E2611">
+        <v>3177.66</v>
+      </c>
+      <c r="F2611">
+        <v>15888.3</v>
+      </c>
+      <c r="G2611" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2611" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2612" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2612" s="1">
+        <v>46115</v>
+      </c>
+      <c r="B2612" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2612" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2612">
+        <v>4</v>
+      </c>
+      <c r="E2612">
+        <v>5622.44</v>
+      </c>
+      <c r="F2612">
+        <v>22489.759999999998</v>
+      </c>
+      <c r="G2612" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2612" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2613" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2613" s="1">
+        <v>46115</v>
+      </c>
+      <c r="B2613" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2613" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2613">
+        <v>6</v>
+      </c>
+      <c r="E2613">
+        <v>2088.5500000000002</v>
+      </c>
+      <c r="F2613">
+        <v>12531.3</v>
+      </c>
+      <c r="G2613" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2613" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2614" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2614" s="1">
+        <v>46116</v>
+      </c>
+      <c r="B2614" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2614" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2614">
+        <v>8</v>
+      </c>
+      <c r="E2614">
+        <v>1799.33</v>
+      </c>
+      <c r="F2614">
+        <v>14394.64</v>
+      </c>
+      <c r="G2614" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2614" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2615" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2615" s="1">
+        <v>46116</v>
+      </c>
+      <c r="B2615" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2615" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2615">
+        <v>4</v>
+      </c>
+      <c r="E2615">
+        <v>2788.88</v>
+      </c>
+      <c r="F2615">
+        <v>11155.52</v>
+      </c>
+      <c r="G2615" t="s">
+        <v>48</v>
+      </c>
+      <c r="H2615" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2616" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2616" s="1">
+        <v>46116</v>
+      </c>
+      <c r="B2616" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2616" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2616">
+        <v>7</v>
+      </c>
+      <c r="E2616">
+        <v>194.33</v>
+      </c>
+      <c r="F2616">
+        <v>1360.31</v>
+      </c>
+      <c r="G2616" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2616" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2617" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2617" s="1">
+        <v>46117</v>
+      </c>
+      <c r="B2617" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2617" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2617">
+        <v>5</v>
+      </c>
+      <c r="E2617">
+        <v>12833.44</v>
+      </c>
+      <c r="F2617">
+        <v>64167.199999999997</v>
+      </c>
+      <c r="G2617" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2617" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2618" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2618" s="1">
+        <v>46117</v>
+      </c>
+      <c r="B2618" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2618" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2618">
+        <v>3</v>
+      </c>
+      <c r="E2618">
+        <v>4266.7700000000004</v>
+      </c>
+      <c r="F2618">
+        <v>12800.31</v>
+      </c>
+      <c r="G2618" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2618" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2619" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2619" s="1">
+        <v>46117</v>
+      </c>
+      <c r="B2619" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2619" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2619">
+        <v>7</v>
+      </c>
+      <c r="E2619">
+        <v>1655.22</v>
+      </c>
+      <c r="F2619">
+        <v>11586.54</v>
+      </c>
+      <c r="G2619" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2619" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2620" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2620" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B2620" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2620" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2620">
+        <v>5</v>
+      </c>
+      <c r="E2620">
+        <v>1444.66</v>
+      </c>
+      <c r="F2620">
+        <v>7223.3</v>
+      </c>
+      <c r="G2620" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2620" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2621" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2621" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B2621" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2621" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2621">
+        <v>4</v>
+      </c>
+      <c r="E2621">
+        <v>1188.8800000000001</v>
+      </c>
+      <c r="F2621">
+        <v>4755.5200000000004</v>
+      </c>
+      <c r="G2621" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2621" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2622" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2622" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B2622" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2622" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2622">
+        <v>6</v>
+      </c>
+      <c r="E2622">
+        <v>3677.33</v>
+      </c>
+      <c r="F2622">
+        <v>22063.98</v>
+      </c>
+      <c r="G2622" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2622" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2623" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2623" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B2623" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2623" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2623">
+        <v>9</v>
+      </c>
+      <c r="E2623">
+        <v>6377.44</v>
+      </c>
+      <c r="F2623">
+        <v>57396.959999999999</v>
+      </c>
+      <c r="G2623" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2623" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2624" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2624" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B2624" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2624" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2624">
+        <v>3</v>
+      </c>
+      <c r="E2624">
+        <v>4844.55</v>
+      </c>
+      <c r="F2624">
+        <v>14533.65</v>
+      </c>
+      <c r="G2624" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2624" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2625" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2625" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B2625" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2625" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2625">
+        <v>4</v>
+      </c>
+      <c r="E2625">
+        <v>8333.2199999999993</v>
+      </c>
+      <c r="F2625">
+        <v>33332.879999999997</v>
+      </c>
+      <c r="G2625" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2625" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2626" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2626" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B2626" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2626" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2626">
+        <v>7</v>
+      </c>
+      <c r="E2626">
+        <v>2122.66</v>
+      </c>
+      <c r="F2626">
+        <v>14858.62</v>
+      </c>
+      <c r="G2626" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2626" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2627" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2627" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B2627" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2627" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2627">
+        <v>6</v>
+      </c>
+      <c r="E2627">
+        <v>683.44</v>
+      </c>
+      <c r="F2627">
+        <v>4100.6400000000003</v>
+      </c>
+      <c r="G2627" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2627" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2628" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2628" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B2628" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2628" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2628">
+        <v>3</v>
+      </c>
+      <c r="E2628">
+        <v>944.77</v>
+      </c>
+      <c r="F2628">
+        <v>2834.31</v>
+      </c>
+      <c r="G2628" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2628" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2629" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2629" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B2629" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2629" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2629">
+        <v>8</v>
+      </c>
+      <c r="E2629">
+        <v>5755.88</v>
+      </c>
+      <c r="F2629">
+        <v>46047.040000000001</v>
+      </c>
+      <c r="G2629" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2629" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2630" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2630" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B2630" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2630" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2630">
+        <v>5</v>
+      </c>
+      <c r="E2630">
+        <v>3744.33</v>
+      </c>
+      <c r="F2630">
+        <v>18721.650000000001</v>
+      </c>
+      <c r="G2630" t="s">
+        <v>48</v>
+      </c>
+      <c r="H2630" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2631" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2631" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B2631" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2631" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2631">
+        <v>7</v>
+      </c>
+      <c r="E2631">
+        <v>1833.55</v>
+      </c>
+      <c r="F2631">
+        <v>12834.85</v>
+      </c>
+      <c r="G2631" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2631" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2632" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2632" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B2632" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2632" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2632">
+        <v>3</v>
+      </c>
+      <c r="E2632">
+        <v>13177.66</v>
+      </c>
+      <c r="F2632">
+        <v>39532.980000000003</v>
+      </c>
+      <c r="G2632" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2632" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2633" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2633" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B2633" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2633" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2633">
+        <v>9</v>
+      </c>
+      <c r="E2633">
+        <v>3033.22</v>
+      </c>
+      <c r="F2633">
+        <v>27298.98</v>
+      </c>
+      <c r="G2633" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2633" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2634" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2634" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B2634" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2634" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2634">
+        <v>5</v>
+      </c>
+      <c r="E2634">
+        <v>2111.44</v>
+      </c>
+      <c r="F2634">
+        <v>10557.2</v>
+      </c>
+      <c r="G2634" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2634" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2635" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2635" s="1">
+        <v>46123</v>
+      </c>
+      <c r="B2635" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2635" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2635">
+        <v>7</v>
+      </c>
+      <c r="E2635">
+        <v>4199.88</v>
+      </c>
+      <c r="F2635">
+        <v>29399.16</v>
+      </c>
+      <c r="G2635" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2635" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2636" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2636" s="1">
+        <v>46123</v>
+      </c>
+      <c r="B2636" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2636" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2636">
+        <v>4</v>
+      </c>
+      <c r="E2636">
+        <v>1377.55</v>
+      </c>
+      <c r="F2636">
+        <v>5510.2</v>
+      </c>
+      <c r="G2636" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2636" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2637" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2637" s="1">
+        <v>46123</v>
+      </c>
+      <c r="B2637" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2637" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2637">
+        <v>6</v>
+      </c>
+      <c r="E2637">
+        <v>7088.22</v>
+      </c>
+      <c r="F2637">
+        <v>42529.32</v>
+      </c>
+      <c r="G2637" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2637" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2638" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2638" s="1">
+        <v>46124</v>
+      </c>
+      <c r="B2638" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2638" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2638">
+        <v>5</v>
+      </c>
+      <c r="E2638">
+        <v>2922.44</v>
+      </c>
+      <c r="F2638">
+        <v>14612.2</v>
+      </c>
+      <c r="G2638" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2638" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2639" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2639" s="1">
+        <v>46124</v>
+      </c>
+      <c r="B2639" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2639" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2639">
+        <v>8</v>
+      </c>
+      <c r="E2639">
+        <v>1733.88</v>
+      </c>
+      <c r="F2639">
+        <v>13871.04</v>
+      </c>
+      <c r="G2639" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2639" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2640" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2640" s="1">
+        <v>46124</v>
+      </c>
+      <c r="B2640" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2640" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2640">
+        <v>4</v>
+      </c>
+      <c r="E2640">
+        <v>189.55</v>
+      </c>
+      <c r="F2640">
+        <v>758.2</v>
+      </c>
+      <c r="G2640" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2640" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2641" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2641" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B2641" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2641" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2641">
+        <v>6</v>
+      </c>
+      <c r="E2641">
+        <v>6544.77</v>
+      </c>
+      <c r="F2641">
+        <v>39268.620000000003</v>
+      </c>
+      <c r="G2641" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2641" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2642" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2642" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B2642" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2642" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2642">
+        <v>7</v>
+      </c>
+      <c r="E2642">
+        <v>1166.33</v>
+      </c>
+      <c r="F2642">
+        <v>8164.31</v>
+      </c>
+      <c r="G2642" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2642" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2643" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2643" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B2643" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2643" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2643">
+        <v>3</v>
+      </c>
+      <c r="E2643">
+        <v>3811.55</v>
+      </c>
+      <c r="F2643">
+        <v>11434.65</v>
+      </c>
+      <c r="G2643" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2643" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2644" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2644" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B2644" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2644" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2644">
+        <v>5</v>
+      </c>
+      <c r="E2644">
+        <v>2144.88</v>
+      </c>
+      <c r="F2644">
+        <v>10724.4</v>
+      </c>
+      <c r="G2644" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2644" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2645" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2645" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B2645" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2645" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2645">
+        <v>4</v>
+      </c>
+      <c r="E2645">
+        <v>13088.22</v>
+      </c>
+      <c r="F2645">
+        <v>52352.88</v>
+      </c>
+      <c r="G2645" t="s">
+        <v>48</v>
+      </c>
+      <c r="H2645" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2646" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2646" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B2646" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2646" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2646">
+        <v>6</v>
+      </c>
+      <c r="E2646">
+        <v>1766.77</v>
+      </c>
+      <c r="F2646">
+        <v>10600.62</v>
+      </c>
+      <c r="G2646" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2646" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2647" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2647" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B2647" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2647" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2647">
+        <v>8</v>
+      </c>
+      <c r="E2647">
+        <v>3633.44</v>
+      </c>
+      <c r="F2647">
+        <v>29067.52</v>
+      </c>
+      <c r="G2647" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2647" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2648" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2648" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B2648" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2648" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2648">
+        <v>3</v>
+      </c>
+      <c r="E2648">
+        <v>4722.88</v>
+      </c>
+      <c r="F2648">
+        <v>14168.64</v>
+      </c>
+      <c r="G2648" t="s">
+        <v>54</v>
+      </c>
+      <c r="H2648" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2649" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2649" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B2649" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2649" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2649">
+        <v>2</v>
+      </c>
+      <c r="E2649">
+        <v>8466.33</v>
+      </c>
+      <c r="F2649">
+        <v>16932.66</v>
+      </c>
+      <c r="G2649" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2649" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2650" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2650" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B2650" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2650" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2650">
+        <v>7</v>
+      </c>
+      <c r="E2650">
+        <v>1466.55</v>
+      </c>
+      <c r="F2650">
+        <v>10265.85</v>
+      </c>
+      <c r="G2650" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2650" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2651" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2651" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B2651" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2651" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2651">
+        <v>5</v>
+      </c>
+      <c r="E2651">
+        <v>4344.22</v>
+      </c>
+      <c r="F2651">
+        <v>21721.1</v>
+      </c>
+      <c r="G2651" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2651" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2652" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2652" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B2652" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2652" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2652">
+        <v>4</v>
+      </c>
+      <c r="E2652">
+        <v>7155.66</v>
+      </c>
+      <c r="F2652">
+        <v>28622.639999999999</v>
+      </c>
+      <c r="G2652" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2652" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2653" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2653" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B2653" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2653" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2653">
+        <v>6</v>
+      </c>
+      <c r="E2653">
+        <v>922.44</v>
+      </c>
+      <c r="F2653">
+        <v>5534.64</v>
+      </c>
+      <c r="G2653" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2653" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2654" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2654" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B2654" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2654" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2654">
+        <v>9</v>
+      </c>
+      <c r="E2654">
+        <v>676.88</v>
+      </c>
+      <c r="F2654">
+        <v>6091.92</v>
+      </c>
+      <c r="G2654" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2654" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2655" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2655" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B2655" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2655" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2655">
+        <v>5</v>
+      </c>
+      <c r="E2655">
+        <v>5873.17</v>
+      </c>
+      <c r="F2655">
+        <v>29365.85</v>
+      </c>
+      <c r="G2655" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2655" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
